--- a/data/trans_orig/IP16B05-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP16B05-Estudios-trans_orig.xlsx
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>4685</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>59,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>13855</t>
+          <t>13400</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>83,14%</t>
+          <t>80,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2809</t>
+          <t>3264</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1278,7 +1278,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>19,59%</t>
         </is>
       </c>
     </row>
@@ -1761,7 +1761,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7981</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>71,73%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1831,7 +1831,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>22577</t>
+          <t>22584</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3154</t>
+          <t>3174</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3260</t>
+          <t>3253</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,59%</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9890</t>
+          <t>10338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -2728,7 +2728,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>76,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27086</t>
+          <t>26606</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -2763,7 +2763,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>90,45%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3592</t>
+          <t>3144</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>3340</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>11,15%</t>
         </is>
       </c>
     </row>
@@ -3399,7 +3399,7 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>17595</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
@@ -3414,7 +3414,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>43304</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3127</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3532,7 +3532,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3536</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
